--- a/backend/zt-checklist.xlsx
+++ b/backend/zt-checklist.xlsx
@@ -13316,42 +13316,42 @@
       </c>
       <c r="D219" s="15" t="inlineStr">
         <is>
-          <t>애플리케이션 배포 전 수동으로 코드 검토 및 취약점 검사를 수행하는가?</t>
+          <t>GitHub repo 소스 코드에 대한 자동 취약점 스캔이 수행되는가?</t>
         </is>
       </c>
       <c r="E219" s="21" t="inlineStr">
         <is>
-          <t>수동</t>
+          <t>자동</t>
         </is>
       </c>
       <c r="F219" s="22" t="inlineStr">
         <is>
-          <t>수동</t>
+          <t>Trivy (래퍼 필요)</t>
         </is>
       </c>
       <c r="G219" s="15" t="inlineStr">
         <is>
-          <t>수동 코드 검토·취약점 점검 기록 존재 여부</t>
+          <t>trivy repo 스캔 결과 (Critical/High 취약점 수)</t>
         </is>
       </c>
       <c r="H219" s="15" t="inlineStr">
         <is>
-          <t>기록 존재 → 충족 / 미존재 → 미충족</t>
+          <t>스캔 수행 AND Critical+High = 0 → 충족 / Critical+High ≤ 5 → 부분 충족 / 그 외 → 미충족</t>
         </is>
       </c>
       <c r="I219" s="19" t="inlineStr">
         <is>
-          <t>해당 없음</t>
+          <t>severity_counts.CRITICAL, severity_counts.HIGH (per package)</t>
         </is>
       </c>
       <c r="J219" s="19" t="inlineStr">
         <is>
-          <t>해당 없음</t>
+          <t>분자: CRITICAL+HIGH 합계, 분모: 1 (지표=절대수)</t>
         </is>
       </c>
       <c r="K219" s="20" t="inlineStr">
         <is>
-          <t>증빙 미제출 → 미충족</t>
+          <t>저장소 미입력/접근 불가 → 평가 불가 / 타임아웃(300초) → 평가 불가</t>
         </is>
       </c>
     </row>
@@ -14406,42 +14406,42 @@
       </c>
       <c r="D238" s="15" t="inlineStr">
         <is>
-          <t>개발 프로세스에 보안 코딩 표준이 적용되어 있는가?</t>
+          <t>소스 코드 내 노출된 비밀번호·API key·토큰이 자동 검출되어 차단되는가?</t>
         </is>
       </c>
       <c r="E238" s="21" t="inlineStr">
         <is>
-          <t>수동</t>
+          <t>자동</t>
         </is>
       </c>
       <c r="F238" s="22" t="inlineStr">
         <is>
-          <t>수동</t>
+          <t>Trivy (래퍼 필요)</t>
         </is>
       </c>
       <c r="G238" s="15" t="inlineStr">
         <is>
-          <t>보안 코딩 표준 문서 존재 여부</t>
+          <t>trivy --scanners secret 스캔 결과 (노출 secret 수)</t>
         </is>
       </c>
       <c r="H238" s="15" t="inlineStr">
         <is>
-          <t>존재 → 충족 / 미존재 → 미충족</t>
+          <t>노출 secret = 0건 → 충족 / 1~3건 → 부분 충족 / 4건 이상 → 미충족</t>
         </is>
       </c>
       <c r="I238" s="19" t="inlineStr">
         <is>
-          <t>해당 없음</t>
+          <t>secrets[].RuleID, secrets[].Severity, secrets[].Target</t>
         </is>
       </c>
       <c r="J238" s="19" t="inlineStr">
         <is>
-          <t>해당 없음</t>
+          <t>분자: 검출된 secret 수, 분모: 1</t>
         </is>
       </c>
       <c r="K238" s="20" t="inlineStr">
         <is>
-          <t>증빙 미제출 → 미충족</t>
+          <t>저장소 미입력 → 평가 불가 / 타임아웃(300초) → 평가 불가</t>
         </is>
       </c>
     </row>
@@ -14463,42 +14463,42 @@
       </c>
       <c r="D239" s="5" t="inlineStr">
         <is>
-          <t>코드 배포 전, 정적이고 수동으로 보안 테스트를 수행하는가?</t>
+          <t>IaC(Dockerfile/Kubernetes/Terraform) 설정 파일에 대한 정적 보안 분석이 자동화되어 있는가?</t>
         </is>
       </c>
       <c r="E239" s="7" t="inlineStr">
         <is>
-          <t>수동</t>
+          <t>자동</t>
         </is>
       </c>
       <c r="F239" s="8" t="inlineStr">
         <is>
-          <t>수동</t>
+          <t>Trivy (래퍼 필요)</t>
         </is>
       </c>
       <c r="G239" s="5" t="inlineStr">
         <is>
-          <t>정적 보안 테스트 기록 존재 여부</t>
+          <t>trivy config / repo --scanners misconfig 결과 (High+Critical 위반 수)</t>
         </is>
       </c>
       <c r="H239" s="5" t="inlineStr">
         <is>
-          <t>기록 존재 → 충족 / 미존재 → 미충족</t>
+          <t>High+Critical 위반 = 0 → 충족 / 1~5건 → 부분 충족 / 6건 이상 → 미충족</t>
         </is>
       </c>
       <c r="I239" s="9" t="inlineStr">
         <is>
-          <t>해당 없음</t>
+          <t>Misconfigurations[].Severity, Misconfigurations[].ID</t>
         </is>
       </c>
       <c r="J239" s="9" t="inlineStr">
         <is>
-          <t>해당 없음</t>
+          <t>분자: severity가 CRITICAL+HIGH인 misconfig 수, 분모: 1</t>
         </is>
       </c>
       <c r="K239" s="10" t="inlineStr">
         <is>
-          <t>증빙 미제출 → 미충족</t>
+          <t>저장소 미입력 → 평가 불가 / 타임아웃(300초) → 평가 불가</t>
         </is>
       </c>
     </row>
@@ -14978,42 +14978,42 @@
       </c>
       <c r="D248" s="15" t="inlineStr">
         <is>
-          <t>최소한의 위험 요소가 식별되고 문서화 하였는가?</t>
+          <t>소프트웨어 위험 요소(취약점·의존성·secret)가 자동 식별되어 가시화되는가?</t>
         </is>
       </c>
       <c r="E248" s="21" t="inlineStr">
         <is>
-          <t>수동</t>
+          <t>자동</t>
         </is>
       </c>
       <c r="F248" s="22" t="inlineStr">
         <is>
-          <t>수동</t>
+          <t>Trivy (래퍼 필요)</t>
         </is>
       </c>
       <c r="G248" s="15" t="inlineStr">
         <is>
-          <t>위험 요소 식별·문서화 자료 존재 여부</t>
+          <t>trivy repo 스캔의 component_count (식별된 위험 요소 수)</t>
         </is>
       </c>
       <c r="H248" s="15" t="inlineStr">
         <is>
-          <t>존재 → 충족 / 미존재 → 미충족</t>
+          <t>식별 결과 ≥ 1건(스캔 자체 수행) → 충족 / 스캔 실패 → 미충족</t>
         </is>
       </c>
       <c r="I248" s="19" t="inlineStr">
         <is>
-          <t>해당 없음</t>
+          <t>Results[], severity_counts (집계)</t>
         </is>
       </c>
       <c r="J248" s="19" t="inlineStr">
         <is>
-          <t>해당 없음</t>
+          <t>분자: 스캔 수행 여부(1/0), 분모: 1</t>
         </is>
       </c>
       <c r="K248" s="20" t="inlineStr">
         <is>
-          <t>증빙 미제출 → 미충족</t>
+          <t>저장소 미입력 → 평가 불가 / 타임아웃(300초) → 평가 불가</t>
         </is>
       </c>
     </row>
@@ -18708,7 +18708,6 @@
         </is>
       </c>
     </row>
-    <row r="7"/>
     <row r="8">
       <c r="A8" s="34" t="inlineStr">
         <is>
@@ -18793,7 +18792,6 @@
         </is>
       </c>
     </row>
-    <row r="15"/>
     <row r="16">
       <c r="A16" s="34" t="inlineStr">
         <is>

--- a/backend/zt-checklist.xlsx
+++ b/backend/zt-checklist.xlsx
@@ -1312,12 +1312,12 @@
       </c>
       <c r="E10" s="7" t="inlineStr">
         <is>
-          <t>수동</t>
+          <t>자동</t>
         </is>
       </c>
       <c r="F10" s="8" t="inlineStr">
         <is>
-          <t>수동</t>
+          <t>web_probe</t>
         </is>
       </c>
       <c r="G10" s="5" t="inlineStr">
@@ -1369,12 +1369,12 @@
       </c>
       <c r="E11" s="7" t="inlineStr">
         <is>
-          <t>수동</t>
+          <t>자동</t>
         </is>
       </c>
       <c r="F11" s="8" t="inlineStr">
         <is>
-          <t>수동</t>
+          <t>web_probe</t>
         </is>
       </c>
       <c r="G11" s="5" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="E16" s="7" t="inlineStr">
         <is>
-          <t>수동</t>
+          <t>자동</t>
         </is>
       </c>
       <c r="F16" s="8" t="inlineStr">
         <is>
-          <t>수동</t>
+          <t>web_probe</t>
         </is>
       </c>
       <c r="G16" s="5" t="inlineStr">
@@ -7959,12 +7959,12 @@
       </c>
       <c r="E125" s="7" t="inlineStr">
         <is>
-          <t>수동</t>
+          <t>자동</t>
         </is>
       </c>
       <c r="F125" s="8" t="inlineStr">
         <is>
-          <t>수동</t>
+          <t>web_probe</t>
         </is>
       </c>
       <c r="G125" s="5" t="inlineStr">
@@ -8016,12 +8016,12 @@
       </c>
       <c r="E126" s="7" t="inlineStr">
         <is>
-          <t>수동</t>
+          <t>자동</t>
         </is>
       </c>
       <c r="F126" s="8" t="inlineStr">
         <is>
-          <t>수동</t>
+          <t>web_probe</t>
         </is>
       </c>
       <c r="G126" s="5" t="inlineStr">
@@ -9102,12 +9102,12 @@
       </c>
       <c r="E145" s="21" t="inlineStr">
         <is>
-          <t>수동</t>
+          <t>자동</t>
         </is>
       </c>
       <c r="F145" s="22" t="inlineStr">
         <is>
-          <t>수동</t>
+          <t>web_probe</t>
         </is>
       </c>
       <c r="G145" s="15" t="inlineStr">
@@ -9216,12 +9216,12 @@
       </c>
       <c r="E147" s="7" t="inlineStr">
         <is>
-          <t>수동</t>
+          <t>자동</t>
         </is>
       </c>
       <c r="F147" s="8" t="inlineStr">
         <is>
-          <t>수동</t>
+          <t>web_probe</t>
         </is>
       </c>
       <c r="G147" s="5" t="inlineStr">
@@ -10185,12 +10185,12 @@
       </c>
       <c r="E164" s="21" t="inlineStr">
         <is>
-          <t>수동</t>
+          <t>자동</t>
         </is>
       </c>
       <c r="F164" s="22" t="inlineStr">
         <is>
-          <t>수동</t>
+          <t>web_probe</t>
         </is>
       </c>
       <c r="G164" s="15" t="inlineStr">
@@ -11496,12 +11496,12 @@
       </c>
       <c r="E187" s="7" t="inlineStr">
         <is>
-          <t>수동</t>
+          <t>자동</t>
         </is>
       </c>
       <c r="F187" s="8" t="inlineStr">
         <is>
-          <t>수동</t>
+          <t>web_probe</t>
         </is>
       </c>
       <c r="G187" s="5" t="inlineStr">
@@ -11895,12 +11895,12 @@
       </c>
       <c r="E194" s="21" t="inlineStr">
         <is>
-          <t>수동</t>
+          <t>자동</t>
         </is>
       </c>
       <c r="F194" s="22" t="inlineStr">
         <is>
-          <t>수동</t>
+          <t>web_probe</t>
         </is>
       </c>
       <c r="G194" s="15" t="inlineStr">
@@ -12465,12 +12465,12 @@
       </c>
       <c r="E204" s="21" t="inlineStr">
         <is>
-          <t>수동</t>
+          <t>자동</t>
         </is>
       </c>
       <c r="F204" s="22" t="inlineStr">
         <is>
-          <t>수동</t>
+          <t>web_probe</t>
         </is>
       </c>
       <c r="G204" s="15" t="inlineStr">
@@ -12522,12 +12522,12 @@
       </c>
       <c r="E205" s="7" t="inlineStr">
         <is>
-          <t>수동</t>
+          <t>자동</t>
         </is>
       </c>
       <c r="F205" s="8" t="inlineStr">
         <is>
-          <t>수동</t>
+          <t>web_probe</t>
         </is>
       </c>
       <c r="G205" s="5" t="inlineStr">
@@ -13378,12 +13378,12 @@
       </c>
       <c r="E220" s="7" t="inlineStr">
         <is>
-          <t>수동</t>
+          <t>자동</t>
         </is>
       </c>
       <c r="F220" s="8" t="inlineStr">
         <is>
-          <t>수동</t>
+          <t>web_probe</t>
         </is>
       </c>
       <c r="G220" s="5" t="inlineStr">
@@ -14126,12 +14126,12 @@
       </c>
       <c r="E233" s="7" t="inlineStr">
         <is>
-          <t>수동</t>
+          <t>자동</t>
         </is>
       </c>
       <c r="F233" s="8" t="inlineStr">
         <is>
-          <t>수동</t>
+          <t>web_probe</t>
         </is>
       </c>
       <c r="G233" s="5" t="inlineStr">
@@ -14812,12 +14812,12 @@
       </c>
       <c r="E245" s="7" t="inlineStr">
         <is>
-          <t>수동</t>
+          <t>자동</t>
         </is>
       </c>
       <c r="F245" s="8" t="inlineStr">
         <is>
-          <t>수동</t>
+          <t>web_probe</t>
         </is>
       </c>
       <c r="G245" s="5" t="inlineStr">
@@ -16356,12 +16356,12 @@
       </c>
       <c r="E272" s="21" t="inlineStr">
         <is>
-          <t>수동</t>
+          <t>자동</t>
         </is>
       </c>
       <c r="F272" s="22" t="inlineStr">
         <is>
-          <t>수동</t>
+          <t>web_probe</t>
         </is>
       </c>
       <c r="G272" s="15" t="inlineStr">
@@ -16413,12 +16413,12 @@
       </c>
       <c r="E273" s="7" t="inlineStr">
         <is>
-          <t>수동</t>
+          <t>자동</t>
         </is>
       </c>
       <c r="F273" s="8" t="inlineStr">
         <is>
-          <t>수동</t>
+          <t>web_probe</t>
         </is>
       </c>
       <c r="G273" s="5" t="inlineStr">
@@ -16756,12 +16756,12 @@
       </c>
       <c r="E279" s="7" t="inlineStr">
         <is>
-          <t>수동</t>
+          <t>자동</t>
         </is>
       </c>
       <c r="F279" s="8" t="inlineStr">
         <is>
-          <t>수동</t>
+          <t>web_probe</t>
         </is>
       </c>
       <c r="G279" s="5" t="inlineStr">
@@ -16813,12 +16813,12 @@
       </c>
       <c r="E280" s="7" t="inlineStr">
         <is>
-          <t>수동</t>
+          <t>자동</t>
         </is>
       </c>
       <c r="F280" s="8" t="inlineStr">
         <is>
-          <t>수동</t>
+          <t>web_probe</t>
         </is>
       </c>
       <c r="G280" s="5" t="inlineStr">
@@ -17212,12 +17212,12 @@
       </c>
       <c r="E287" s="21" t="inlineStr">
         <is>
-          <t>수동</t>
+          <t>자동</t>
         </is>
       </c>
       <c r="F287" s="22" t="inlineStr">
         <is>
-          <t>수동</t>
+          <t>web_probe</t>
         </is>
       </c>
       <c r="G287" s="15" t="inlineStr">
@@ -17269,12 +17269,12 @@
       </c>
       <c r="E288" s="7" t="inlineStr">
         <is>
-          <t>수동</t>
+          <t>자동</t>
         </is>
       </c>
       <c r="F288" s="8" t="inlineStr">
         <is>
-          <t>수동</t>
+          <t>web_probe</t>
         </is>
       </c>
       <c r="G288" s="5" t="inlineStr">
@@ -17725,12 +17725,12 @@
       </c>
       <c r="E296" s="21" t="inlineStr">
         <is>
-          <t>수동</t>
+          <t>자동</t>
         </is>
       </c>
       <c r="F296" s="22" t="inlineStr">
         <is>
-          <t>수동</t>
+          <t>web_probe</t>
         </is>
       </c>
       <c r="G296" s="15" t="inlineStr">
@@ -17782,12 +17782,12 @@
       </c>
       <c r="E297" s="7" t="inlineStr">
         <is>
-          <t>수동</t>
+          <t>자동</t>
         </is>
       </c>
       <c r="F297" s="8" t="inlineStr">
         <is>
-          <t>수동</t>
+          <t>web_probe</t>
         </is>
       </c>
       <c r="G297" s="5" t="inlineStr">
@@ -18295,12 +18295,12 @@
       </c>
       <c r="E306" s="7" t="inlineStr">
         <is>
-          <t>수동</t>
+          <t>자동</t>
         </is>
       </c>
       <c r="F306" s="8" t="inlineStr">
         <is>
-          <t>수동</t>
+          <t>web_probe</t>
         </is>
       </c>
       <c r="G306" s="5" t="inlineStr">

--- a/backend/zt-checklist.xlsx
+++ b/backend/zt-checklist.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="체크리스트_도구매핑" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="범례" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="체크리스트_도구매핑" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="범례" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -6466,12 +6466,12 @@
       </c>
       <c r="E99" s="7" t="inlineStr">
         <is>
-          <t>수동</t>
+          <t>자동</t>
         </is>
       </c>
       <c r="F99" s="8" t="inlineStr">
         <is>
-          <t>수동</t>
+          <t>railway</t>
         </is>
       </c>
       <c r="G99" s="5" t="inlineStr">
@@ -8700,12 +8700,12 @@
       </c>
       <c r="E138" s="7" t="inlineStr">
         <is>
-          <t>수동</t>
+          <t>자동</t>
         </is>
       </c>
       <c r="F138" s="8" t="inlineStr">
         <is>
-          <t>수동</t>
+          <t>railway</t>
         </is>
       </c>
       <c r="G138" s="5" t="inlineStr">
@@ -8757,12 +8757,12 @@
       </c>
       <c r="E139" s="7" t="inlineStr">
         <is>
-          <t>수동</t>
+          <t>자동</t>
         </is>
       </c>
       <c r="F139" s="8" t="inlineStr">
         <is>
-          <t>수동</t>
+          <t>railway</t>
         </is>
       </c>
       <c r="G139" s="5" t="inlineStr">
@@ -10299,12 +10299,12 @@
       </c>
       <c r="E166" s="7" t="inlineStr">
         <is>
-          <t>수동</t>
+          <t>자동</t>
         </is>
       </c>
       <c r="F166" s="8" t="inlineStr">
         <is>
-          <t>수동</t>
+          <t>supabase</t>
         </is>
       </c>
       <c r="G166" s="5" t="inlineStr">
@@ -14069,12 +14069,12 @@
       </c>
       <c r="E232" s="21" t="inlineStr">
         <is>
-          <t>수동</t>
+          <t>자동</t>
         </is>
       </c>
       <c r="F232" s="22" t="inlineStr">
         <is>
-          <t>수동</t>
+          <t>vercel</t>
         </is>
       </c>
       <c r="G232" s="15" t="inlineStr">
@@ -16699,12 +16699,12 @@
       </c>
       <c r="E278" s="21" t="inlineStr">
         <is>
-          <t>수동</t>
+          <t>자동</t>
         </is>
       </c>
       <c r="F278" s="22" t="inlineStr">
         <is>
-          <t>수동</t>
+          <t>supabase</t>
         </is>
       </c>
       <c r="G278" s="15" t="inlineStr">
